--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="61">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -91,19 +91,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>21.16%</t>
+    <t>22.22%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>40.28%</t>
+    <t>41.06%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>5.21%</t>
+    <t>5.44%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -127,13 +127,13 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>95.88%</t>
+    <t>96.77%</t>
   </si>
   <si>
     <t>Preferente1raBase</t>
   </si>
   <si>
-    <t>98.60%</t>
+    <t>99.00%</t>
   </si>
   <si>
     <t>Preferente3raBase</t>
@@ -157,19 +157,19 @@
     <t>Superior</t>
   </si>
   <si>
-    <t>81.95%</t>
+    <t>83.21%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>63.27%</t>
+    <t>64.66%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>69.72%</t>
+    <t>71.25%</t>
   </si>
   <si>
     <t>ToroBar</t>
@@ -193,7 +193,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>51.37%</t>
+    <t>52.10%</t>
   </si>
 </sst>
 </file>
@@ -801,7 +801,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="7">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="L7" s="7">
         <v>2</v>
@@ -819,10 +819,10 @@
         <v>2372</v>
       </c>
       <c r="Q7" s="7">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="R7" s="7">
-        <v>1870</v>
+        <v>1845</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>26</v>
@@ -860,7 +860,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="7">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>23</v>
@@ -878,10 +878,10 @@
         <v>2170</v>
       </c>
       <c r="Q8" s="7">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="R8" s="7">
-        <v>1296</v>
+        <v>1279</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>28</v>
@@ -919,7 +919,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="7">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>23</v>
@@ -937,10 +937,10 @@
         <v>3145</v>
       </c>
       <c r="Q9" s="7">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="R9" s="7">
-        <v>2981</v>
+        <v>2974</v>
       </c>
       <c r="S9" s="8" t="s">
         <v>30</v>
@@ -1130,8 +1130,8 @@
       <c r="B13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>23</v>
+      <c r="C13" s="7">
+        <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>23</v>
@@ -1143,7 +1143,7 @@
         <v>23</v>
       </c>
       <c r="G13" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>23</v>
@@ -1155,7 +1155,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="7">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L13" s="7">
         <v>61</v>
@@ -1167,16 +1167,16 @@
         <v>23</v>
       </c>
       <c r="O13" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="P13" s="7">
         <v>1794</v>
       </c>
       <c r="Q13" s="7">
-        <v>1720</v>
+        <v>1736</v>
       </c>
       <c r="R13" s="7">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="S13" s="8" t="s">
         <v>38</v>
@@ -1214,7 +1214,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L14" s="7">
         <v>3</v>
@@ -1232,10 +1232,10 @@
         <v>499</v>
       </c>
       <c r="Q14" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="R14" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S14" s="8" t="s">
         <v>40</v>
@@ -1432,7 +1432,7 @@
         <v>23</v>
       </c>
       <c r="E18" s="7">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>23</v>
@@ -1450,7 +1450,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="7">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="L18" s="7">
         <v>3</v>
@@ -1468,10 +1468,10 @@
         <v>2299</v>
       </c>
       <c r="Q18" s="7">
-        <v>1884</v>
+        <v>1913</v>
       </c>
       <c r="R18" s="7">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="S18" s="8" t="s">
         <v>48</v>
@@ -1509,7 +1509,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="7">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="L19" s="7">
         <v>4</v>
@@ -1527,10 +1527,10 @@
         <v>648</v>
       </c>
       <c r="Q19" s="7">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="R19" s="7">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="S19" s="8" t="s">
         <v>50</v>
@@ -1540,8 +1540,8 @@
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="7">
-        <v>4</v>
+      <c r="B20" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>23</v>
@@ -1568,7 +1568,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="7">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="L20" s="7">
         <v>2</v>
@@ -1579,17 +1579,17 @@
       <c r="N20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>23</v>
+      <c r="O20" s="7">
+        <v>6</v>
       </c>
       <c r="P20" s="7">
         <v>786</v>
       </c>
       <c r="Q20" s="7">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="R20" s="7">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="S20" s="8" t="s">
         <v>52</v>
@@ -1609,7 +1609,7 @@
         <v>23</v>
       </c>
       <c r="E21" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>23</v>
@@ -1639,7 +1639,7 @@
         <v>23</v>
       </c>
       <c r="O21" s="7">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P21" s="7">
         <v>245</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="61">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -91,7 +91,7 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>22.22%</t>
+    <t>22.30%</t>
   </si>
   <si>
     <t>General Superior</t>
@@ -193,7 +193,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>52.10%</t>
+    <t>52.11%</t>
   </si>
 </sst>
 </file>
@@ -773,8 +773,8 @@
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>23</v>
+      <c r="B7" s="7">
+        <v>2</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>23</v>
@@ -819,10 +819,10 @@
         <v>2372</v>
       </c>
       <c r="Q7" s="7">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="R7" s="7">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>26</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="61">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -91,19 +91,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>31.45%</t>
+    <t>33.01%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>45.12%</t>
+    <t>46.82%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>6.68%</t>
+    <t>6.80%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -127,19 +127,19 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>98.22%</t>
+    <t>98.49%</t>
   </si>
   <si>
     <t>Preferente1raBase</t>
   </si>
   <si>
-    <t>99.20%</t>
+    <t>99.40%</t>
   </si>
   <si>
     <t>Preferente3raBase</t>
   </si>
   <si>
-    <t>97.91%</t>
+    <t>98.51%</t>
   </si>
   <si>
     <t>Suite ToroGrill</t>
@@ -151,25 +151,25 @@
     <t>Suites</t>
   </si>
   <si>
-    <t>65.75%</t>
+    <t>69.69%</t>
   </si>
   <si>
     <t>Superior</t>
   </si>
   <si>
-    <t>87.56%</t>
+    <t>88.60%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>80.86%</t>
+    <t>85.03%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>80.41%</t>
+    <t>84.99%</t>
   </si>
   <si>
     <t>ToroBar</t>
@@ -187,13 +187,13 @@
     <t>Zona Móbil</t>
   </si>
   <si>
-    <t>30.77%</t>
+    <t>38.46%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>56.31%</t>
+    <t>57.49%</t>
   </si>
 </sst>
 </file>
@@ -773,8 +773,8 @@
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
-        <v>3</v>
+      <c r="B7" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>23</v>
@@ -801,7 +801,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="7">
-        <v>677</v>
+        <v>717</v>
       </c>
       <c r="L7" s="7">
         <v>2</v>
@@ -819,10 +819,10 @@
         <v>2372</v>
       </c>
       <c r="Q7" s="7">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="R7" s="7">
-        <v>1626</v>
+        <v>1589</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>26</v>
@@ -860,7 +860,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="7">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>23</v>
@@ -878,10 +878,10 @@
         <v>2170</v>
       </c>
       <c r="Q8" s="7">
-        <v>979</v>
+        <v>1016</v>
       </c>
       <c r="R8" s="7">
-        <v>1191</v>
+        <v>1154</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>28</v>
@@ -919,7 +919,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>23</v>
@@ -937,10 +937,10 @@
         <v>3145</v>
       </c>
       <c r="Q9" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="R9" s="7">
-        <v>2935</v>
+        <v>2931</v>
       </c>
       <c r="S9" s="8" t="s">
         <v>30</v>
@@ -1131,13 +1131,13 @@
         <v>23</v>
       </c>
       <c r="C13" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="7">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>23</v>
@@ -1155,7 +1155,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="7">
-        <v>740</v>
+        <v>758</v>
       </c>
       <c r="L13" s="7">
         <v>63</v>
@@ -1167,16 +1167,16 @@
         <v>23</v>
       </c>
       <c r="O13" s="7">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="P13" s="7">
         <v>1794</v>
       </c>
       <c r="Q13" s="7">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="R13" s="7">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="S13" s="8" t="s">
         <v>38</v>
@@ -1214,7 +1214,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L14" s="7">
         <v>5</v>
@@ -1232,10 +1232,10 @@
         <v>499</v>
       </c>
       <c r="Q14" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="R14" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" s="8" t="s">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>23</v>
@@ -1291,10 +1291,10 @@
         <v>671</v>
       </c>
       <c r="Q15" s="7">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="R15" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S15" s="8" t="s">
         <v>42</v>
@@ -1366,8 +1366,8 @@
       <c r="B17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>23</v>
+      <c r="C17" s="7">
+        <v>10</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>23</v>
@@ -1409,10 +1409,10 @@
         <v>254</v>
       </c>
       <c r="Q17" s="7">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="R17" s="7">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="S17" s="8" t="s">
         <v>46</v>
@@ -1426,13 +1426,13 @@
         <v>23</v>
       </c>
       <c r="C18" s="7">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>23</v>
@@ -1450,7 +1450,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="7">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="L18" s="7">
         <v>7</v>
@@ -1462,16 +1462,16 @@
         <v>23</v>
       </c>
       <c r="O18" s="7">
-        <v>691</v>
+        <v>625</v>
       </c>
       <c r="P18" s="7">
         <v>2299</v>
       </c>
       <c r="Q18" s="7">
-        <v>2013</v>
+        <v>2037</v>
       </c>
       <c r="R18" s="7">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="S18" s="8" t="s">
         <v>48</v>
@@ -1497,7 +1497,7 @@
         <v>23</v>
       </c>
       <c r="G19" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>23</v>
@@ -1509,7 +1509,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="7">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="L19" s="7">
         <v>4</v>
@@ -1521,16 +1521,16 @@
         <v>23</v>
       </c>
       <c r="O19" s="7">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="P19" s="7">
         <v>648</v>
       </c>
       <c r="Q19" s="7">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="R19" s="7">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="S19" s="8" t="s">
         <v>50</v>
@@ -1543,8 +1543,8 @@
       <c r="B20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>23</v>
+      <c r="C20" s="7">
+        <v>4</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>23</v>
@@ -1568,7 +1568,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="7">
-        <v>564</v>
+        <v>596</v>
       </c>
       <c r="L20" s="7">
         <v>2</v>
@@ -1586,10 +1586,10 @@
         <v>786</v>
       </c>
       <c r="Q20" s="7">
-        <v>632</v>
+        <v>668</v>
       </c>
       <c r="R20" s="7">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="S20" s="8" t="s">
         <v>52</v>
@@ -1602,14 +1602,14 @@
       <c r="B21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>23</v>
+      <c r="C21" s="7">
+        <v>72</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="7">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>23</v>
@@ -1639,7 +1639,7 @@
         <v>23</v>
       </c>
       <c r="O21" s="7">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="P21" s="7">
         <v>245</v>
@@ -1726,8 +1726,8 @@
       <c r="D23" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>23</v>
+      <c r="E23" s="7">
+        <v>5</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>23</v>
@@ -1763,10 +1763,10 @@
         <v>65</v>
       </c>
       <c r="Q23" s="7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R23" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="S23" s="8" t="s">
         <v>58</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="60">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>38.79%</t>
+    <t>41.36%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>48.39%</t>
+    <t>49.22%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>7.60%</t>
+    <t>8.01%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -124,7 +124,7 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>98.72%</t>
+    <t>98.89%</t>
   </si>
   <si>
     <t>Preferente1raBase</t>
@@ -154,19 +154,19 @@
     <t>Superior</t>
   </si>
   <si>
-    <t>89.52%</t>
+    <t>93.43%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>91.20%</t>
+    <t>96.76%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>89.57%</t>
+    <t>94.66%</t>
   </si>
   <si>
     <t>ToroBar</t>
@@ -190,7 +190,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>59.53%</t>
+    <t>61.16%</t>
   </si>
 </sst>
 </file>
@@ -783,7 +783,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>845</v>
+        <v>904</v>
       </c>
       <c r="L7" s="6">
         <v>2</v>
@@ -794,14 +794,14 @@
       <c r="N7" s="6">
         <v>64</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="O7" s="6">
+        <v>2</v>
       </c>
       <c r="P7" s="6">
-        <v>920</v>
+        <v>981</v>
       </c>
       <c r="Q7" s="6">
-        <v>1452</v>
+        <v>1391</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -839,7 +839,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -854,10 +854,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1050</v>
+        <v>1068</v>
       </c>
       <c r="Q8" s="6">
-        <v>1120</v>
+        <v>1102</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -895,7 +895,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -906,14 +906,14 @@
       <c r="N9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
+      <c r="O9" s="6">
+        <v>1</v>
       </c>
       <c r="P9" s="6">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="Q9" s="6">
-        <v>2906</v>
+        <v>2893</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1095,13 +1095,13 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1119,7 +1119,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="L13" s="6">
         <v>64</v>
@@ -1128,16 +1128,16 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>398</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
+        <v>357</v>
+      </c>
+      <c r="O13" s="6">
+        <v>1</v>
       </c>
       <c r="P13" s="6">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="Q13" s="6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1325,7 +1325,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="6">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1352,7 +1352,7 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
@@ -1375,13 +1375,13 @@
         <v>2299</v>
       </c>
       <c r="C18" s="6">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>254</v>
+        <v>389</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1402,22 +1402,22 @@
         <v>836</v>
       </c>
       <c r="L18" s="6">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>583</v>
+        <v>504</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2058</v>
+        <v>2148</v>
       </c>
       <c r="Q18" s="6">
-        <v>241</v>
+        <v>151</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>47</v>
@@ -1455,10 +1455,10 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="L19" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>22</v>
@@ -1466,14 +1466,14 @@
       <c r="N19" s="6">
         <v>93</v>
       </c>
-      <c r="O19" s="6" t="s">
-        <v>22</v>
+      <c r="O19" s="6">
+        <v>3</v>
       </c>
       <c r="P19" s="6">
-        <v>591</v>
+        <v>627</v>
       </c>
       <c r="Q19" s="6">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>
@@ -1511,7 +1511,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="6">
-        <v>628</v>
+        <v>668</v>
       </c>
       <c r="L20" s="6">
         <v>2</v>
@@ -1526,10 +1526,10 @@
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>704</v>
+        <v>744</v>
       </c>
       <c r="Q20" s="6">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>51</v>
@@ -1549,7 +1549,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="6">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1576,7 +1576,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="60">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>41.36%</t>
+    <t>43.51%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>49.22%</t>
+    <t>50.09%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>8.01%</t>
+    <t>8.39%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -136,7 +136,7 @@
     <t>Preferente3raBase</t>
   </si>
   <si>
-    <t>99.25%</t>
+    <t>99.70%</t>
   </si>
   <si>
     <t>Suite ToroGrill</t>
@@ -160,13 +160,13 @@
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>96.76%</t>
+    <t>96.60%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>94.66%</t>
+    <t>96.95%</t>
   </si>
   <si>
     <t>ToroBar</t>
@@ -190,7 +190,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.16%</t>
+    <t>61.79%</t>
   </si>
 </sst>
 </file>
@@ -783,7 +783,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>904</v>
+        <v>957</v>
       </c>
       <c r="L7" s="6">
         <v>2</v>
@@ -794,14 +794,14 @@
       <c r="N7" s="6">
         <v>64</v>
       </c>
-      <c r="O7" s="6">
-        <v>2</v>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>981</v>
+        <v>1032</v>
       </c>
       <c r="Q7" s="6">
-        <v>1391</v>
+        <v>1340</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -839,7 +839,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>706</v>
+        <v>725</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -854,10 +854,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1068</v>
+        <v>1087</v>
       </c>
       <c r="Q8" s="6">
-        <v>1102</v>
+        <v>1083</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -895,7 +895,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -906,14 +906,14 @@
       <c r="N9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="6">
-        <v>1</v>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="Q9" s="6">
-        <v>2893</v>
+        <v>2881</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1095,7 +1095,7 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1119,7 +1119,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="L13" s="6">
         <v>64</v>
@@ -1128,10 +1128,10 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>357</v>
-      </c>
-      <c r="O13" s="6">
-        <v>1</v>
+        <v>371</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
         <v>1774</v>
@@ -1231,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>22</v>
@@ -1246,10 +1246,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="Q15" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1455,7 +1455,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L19" s="6">
         <v>6</v>
@@ -1466,14 +1466,14 @@
       <c r="N19" s="6">
         <v>93</v>
       </c>
-      <c r="O19" s="6">
-        <v>3</v>
+      <c r="O19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="Q19" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>
@@ -1511,7 +1511,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="6">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="L20" s="6">
         <v>2</v>
@@ -1526,10 +1526,10 @@
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="Q20" s="6">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>51</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="59">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>43.51%</t>
+    <t>44.10%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>50.09%</t>
+    <t>50.32%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>8.39%</t>
+    <t>8.90%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -130,7 +130,7 @@
     <t>Preferente1raBase</t>
   </si>
   <si>
-    <t>99.60%</t>
+    <t>99.20%</t>
   </si>
   <si>
     <t>Preferente3raBase</t>
@@ -160,15 +160,12 @@
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>96.60%</t>
+    <t>97.07%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>96.95%</t>
-  </si>
-  <si>
     <t>ToroBar</t>
   </si>
   <si>
@@ -190,7 +187,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.79%</t>
+    <t>62.02%</t>
   </si>
 </sst>
 </file>
@@ -783,7 +780,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="L7" s="6">
         <v>2</v>
@@ -794,14 +791,14 @@
       <c r="N7" s="6">
         <v>64</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="O7" s="6">
+        <v>6</v>
       </c>
       <c r="P7" s="6">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="Q7" s="6">
-        <v>1340</v>
+        <v>1326</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -839,7 +836,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -854,10 +851,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="Q8" s="6">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -895,7 +892,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -910,10 +907,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="Q9" s="6">
-        <v>2881</v>
+        <v>2865</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1095,13 +1092,13 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1119,16 +1116,16 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="L13" s="6">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>371</v>
+        <v>308</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
@@ -1163,7 +1160,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>22</v>
@@ -1184,16 +1181,16 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>14</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="O14" s="6">
+        <v>10</v>
       </c>
       <c r="P14" s="6">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q14" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>39</v>
@@ -1231,7 +1228,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>22</v>
@@ -1240,7 +1237,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1375,13 +1372,13 @@
         <v>2299</v>
       </c>
       <c r="C18" s="6">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1408,7 +1405,7 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
@@ -1455,7 +1452,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="L19" s="6">
         <v>6</v>
@@ -1464,16 +1461,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="Q19" s="6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>
@@ -1511,7 +1508,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="6">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L20" s="6">
         <v>2</v>
@@ -1526,18 +1523,18 @@
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="Q20" s="6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="6">
         <v>245</v>
@@ -1549,7 +1546,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="6">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1576,7 +1573,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
@@ -1588,12 +1585,12 @@
         <v>92</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="6">
         <v>344</v>
@@ -1644,12 +1641,12 @@
         <v>302</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="6">
         <v>65</v>
@@ -1700,12 +1697,12 @@
         <v>40</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="7">
         <f>SUM(B6:B23)</f>
@@ -1756,7 +1753,7 @@
         <f>SUM(Q6:Q23)</f>
       </c>
       <c r="R24" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="60">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>44.10%</t>
+    <t>49.45%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>50.32%</t>
+    <t>59.31%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>8.90%</t>
+    <t>9.41%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -112,7 +112,7 @@
     <t>Palcos Superior</t>
   </si>
   <si>
-    <t>89.47%</t>
+    <t>73.68%</t>
   </si>
   <si>
     <t>PalcosLaterales</t>
@@ -124,19 +124,19 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>98.89%</t>
+    <t>99.00%</t>
   </si>
   <si>
     <t>Preferente1raBase</t>
   </si>
   <si>
-    <t>99.20%</t>
+    <t>99.60%</t>
   </si>
   <si>
     <t>Preferente3raBase</t>
   </si>
   <si>
-    <t>99.70%</t>
+    <t>99.85%</t>
   </si>
   <si>
     <t>Suite ToroGrill</t>
@@ -154,7 +154,7 @@
     <t>Superior</t>
   </si>
   <si>
-    <t>93.43%</t>
+    <t>94.43%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
@@ -166,6 +166,9 @@
     <t>Superior3raBase</t>
   </si>
   <si>
+    <t>97.33%</t>
+  </si>
+  <si>
     <t>ToroBar</t>
   </si>
   <si>
@@ -187,7 +190,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>62.02%</t>
+    <t>64.21%</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>965</v>
+        <v>1098</v>
       </c>
       <c r="L7" s="6">
         <v>2</v>
@@ -791,14 +794,14 @@
       <c r="N7" s="6">
         <v>64</v>
       </c>
-      <c r="O7" s="6">
-        <v>6</v>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1046</v>
+        <v>1173</v>
       </c>
       <c r="Q7" s="6">
-        <v>1326</v>
+        <v>1199</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -836,7 +839,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>730</v>
+        <v>808</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -845,16 +848,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>342</v>
+        <v>459</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1092</v>
+        <v>1287</v>
       </c>
       <c r="Q8" s="6">
-        <v>1078</v>
+        <v>883</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -892,7 +895,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -907,10 +910,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="Q9" s="6">
-        <v>2865</v>
+        <v>2849</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -986,13 +989,13 @@
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
@@ -1019,10 +1022,10 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q11" s="6">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1092,13 +1095,13 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1116,25 +1119,25 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="L13" s="6">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="Q13" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1160,7 +1163,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>22</v>
@@ -1172,7 +1175,7 @@
         <v>22</v>
       </c>
       <c r="K14" s="6">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L14" s="6">
         <v>5</v>
@@ -1183,14 +1186,14 @@
       <c r="N14" s="6">
         <v>4</v>
       </c>
-      <c r="O14" s="6">
-        <v>10</v>
+      <c r="O14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Q14" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>39</v>
@@ -1203,8 +1206,8 @@
       <c r="B15" s="6">
         <v>671</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>22</v>
+      <c r="C15" s="6">
+        <v>10</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
@@ -1228,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>22</v>
@@ -1237,16 +1240,16 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Q15" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1372,13 +1375,13 @@
         <v>2299</v>
       </c>
       <c r="C18" s="6">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1396,25 +1399,25 @@
         <v>22</v>
       </c>
       <c r="K18" s="6">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="L18" s="6">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>494</v>
+        <v>445</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2148</v>
+        <v>2171</v>
       </c>
       <c r="Q18" s="6">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>47</v>
@@ -1452,7 +1455,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L19" s="6">
         <v>6</v>
@@ -1461,7 +1464,7 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
@@ -1508,7 +1511,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="6">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L20" s="6">
         <v>2</v>
@@ -1523,18 +1526,18 @@
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="Q20" s="6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="6">
         <v>245</v>
@@ -1546,7 +1549,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="6">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1573,7 +1576,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
@@ -1585,12 +1588,12 @@
         <v>92</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" s="6">
         <v>344</v>
@@ -1641,12 +1644,12 @@
         <v>302</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="6">
         <v>65</v>
@@ -1697,12 +1700,12 @@
         <v>40</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" s="7">
         <f>SUM(B6:B23)</f>
@@ -1753,7 +1756,7 @@
         <f>SUM(Q6:Q23)</f>
       </c>
       <c r="R24" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="60">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>49.45%</t>
+    <t>52.19%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>59.31%</t>
+    <t>64.84%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>9.41%</t>
+    <t>9.89%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -148,25 +148,25 @@
     <t>Suites</t>
   </si>
   <si>
-    <t>69.69%</t>
+    <t>67.32%</t>
   </si>
   <si>
     <t>Superior</t>
   </si>
   <si>
-    <t>94.43%</t>
+    <t>96.35%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>97.07%</t>
+    <t>97.22%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>97.33%</t>
+    <t>97.71%</t>
   </si>
   <si>
     <t>ToroBar</t>
@@ -190,7 +190,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>64.21%</t>
+    <t>65.72%</t>
   </si>
 </sst>
 </file>
@@ -783,7 +783,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>1098</v>
+        <v>1163</v>
       </c>
       <c r="L7" s="6">
         <v>2</v>
@@ -798,10 +798,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1173</v>
+        <v>1238</v>
       </c>
       <c r="Q7" s="6">
-        <v>1199</v>
+        <v>1134</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -839,7 +839,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -848,16 +848,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>459</v>
+        <v>549</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1287</v>
+        <v>1407</v>
       </c>
       <c r="Q8" s="6">
-        <v>883</v>
+        <v>763</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -895,7 +895,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -910,10 +910,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="Q9" s="6">
-        <v>2849</v>
+        <v>2834</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1095,13 +1095,13 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1128,7 +1128,7 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
@@ -1231,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>22</v>
@@ -1240,7 +1240,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1325,7 +1325,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1352,16 +1352,16 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="Q17" s="6">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>45</v>
@@ -1381,7 +1381,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1399,7 +1399,7 @@
         <v>22</v>
       </c>
       <c r="K18" s="6">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="L18" s="6">
         <v>54</v>
@@ -1408,16 +1408,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2171</v>
+        <v>2215</v>
       </c>
       <c r="Q18" s="6">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>47</v>
@@ -1430,8 +1430,8 @@
       <c r="B19" s="6">
         <v>648</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>22</v>
+      <c r="C19" s="6">
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
@@ -1455,7 +1455,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L19" s="6">
         <v>6</v>
@@ -1464,16 +1464,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>70</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>22</v>
+        <v>64</v>
+      </c>
+      <c r="O19" s="6">
+        <v>1</v>
       </c>
       <c r="P19" s="6">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="Q19" s="6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>
@@ -1511,7 +1511,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="6">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="L20" s="6">
         <v>2</v>
@@ -1526,10 +1526,10 @@
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="Q20" s="6">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>51</v>
@@ -1549,7 +1549,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="6">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1576,7 +1576,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="58">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>52.19%</t>
+    <t>64.46%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>64.84%</t>
+    <t>73.73%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>9.89%</t>
+    <t>13.48%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -124,21 +124,15 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>99.00%</t>
+    <t>99.72%</t>
   </si>
   <si>
     <t>Preferente1raBase</t>
   </si>
   <si>
-    <t>99.60%</t>
-  </si>
-  <si>
     <t>Preferente3raBase</t>
   </si>
   <si>
-    <t>99.85%</t>
-  </si>
-  <si>
     <t>Suite ToroGrill</t>
   </si>
   <si>
@@ -154,19 +148,19 @@
     <t>Superior</t>
   </si>
   <si>
-    <t>96.35%</t>
+    <t>97.74%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>97.22%</t>
+    <t>98.30%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>97.71%</t>
+    <t>97.84%</t>
   </si>
   <si>
     <t>ToroBar</t>
@@ -190,7 +184,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>65.72%</t>
+    <t>69.78%</t>
   </si>
 </sst>
 </file>
@@ -783,25 +777,25 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>1163</v>
+        <v>1452</v>
       </c>
       <c r="L7" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>64</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+        <v>60</v>
+      </c>
+      <c r="O7" s="6">
+        <v>4</v>
       </c>
       <c r="P7" s="6">
-        <v>1238</v>
+        <v>1529</v>
       </c>
       <c r="Q7" s="6">
-        <v>1134</v>
+        <v>843</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -839,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>838</v>
+        <v>1029</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -850,14 +844,14 @@
       <c r="N8" s="6">
         <v>549</v>
       </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
+      <c r="O8" s="6">
+        <v>2</v>
       </c>
       <c r="P8" s="6">
-        <v>1407</v>
+        <v>1600</v>
       </c>
       <c r="Q8" s="6">
-        <v>763</v>
+        <v>570</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -895,7 +889,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>311</v>
+        <v>421</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -906,14 +900,14 @@
       <c r="N9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
+      <c r="O9" s="6">
+        <v>3</v>
       </c>
       <c r="P9" s="6">
-        <v>311</v>
+        <v>424</v>
       </c>
       <c r="Q9" s="6">
-        <v>2834</v>
+        <v>2721</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1095,7 +1089,7 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1119,25 +1113,25 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="L13" s="6">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>1776</v>
+        <v>1789</v>
       </c>
       <c r="Q13" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1175,7 +1169,7 @@
         <v>22</v>
       </c>
       <c r="K14" s="6">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L14" s="6">
         <v>5</v>
@@ -1190,18 +1184,18 @@
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>497</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>2</v>
+        <v>499</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="6">
         <v>671</v>
@@ -1231,7 +1225,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>22</v>
@@ -1240,24 +1234,24 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>670</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>1</v>
+        <v>671</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="6">
         <v>40</v>
@@ -1308,12 +1302,12 @@
         <v>20</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6">
         <v>254</v>
@@ -1364,24 +1358,24 @@
         <v>83</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6">
         <v>2299</v>
       </c>
       <c r="C18" s="6">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>450</v>
+        <v>507</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1399,7 +1393,7 @@
         <v>22</v>
       </c>
       <c r="K18" s="6">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="L18" s="6">
         <v>54</v>
@@ -1408,24 +1402,24 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>459</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>22</v>
+        <v>405</v>
+      </c>
+      <c r="O18" s="6">
+        <v>1</v>
       </c>
       <c r="P18" s="6">
-        <v>2215</v>
+        <v>2247</v>
       </c>
       <c r="Q18" s="6">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6">
         <v>648</v>
@@ -1455,33 +1449,33 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="L19" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>64</v>
-      </c>
-      <c r="O19" s="6">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="Q19" s="6">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="6">
         <v>786</v>
@@ -1511,7 +1505,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="6">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L20" s="6">
         <v>2</v>
@@ -1526,18 +1520,18 @@
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="Q20" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B21" s="6">
         <v>245</v>
@@ -1588,12 +1582,12 @@
         <v>92</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B22" s="6">
         <v>344</v>
@@ -1644,12 +1638,12 @@
         <v>302</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23" s="6">
         <v>65</v>
@@ -1700,12 +1694,12 @@
         <v>40</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B24" s="7">
         <f>SUM(B6:B23)</f>
@@ -1756,7 +1750,7 @@
         <f>SUM(Q6:Q23)</f>
       </c>
       <c r="R24" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="58">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>64.46%</t>
+    <t>69.44%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>73.73%</t>
+    <t>74.38%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>13.48%</t>
+    <t>14.82%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -124,7 +124,7 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>99.72%</t>
+    <t>99.78%</t>
   </si>
   <si>
     <t>Preferente1raBase</t>
@@ -148,7 +148,7 @@
     <t>Superior</t>
   </si>
   <si>
-    <t>97.74%</t>
+    <t>98.65%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
@@ -166,7 +166,7 @@
     <t>ToroBar</t>
   </si>
   <si>
-    <t>62.45%</t>
+    <t>68.57%</t>
   </si>
   <si>
     <t>ToroGrill</t>
@@ -184,7 +184,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>69.78%</t>
+    <t>71.09%</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -777,7 +777,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>1452</v>
+        <v>1527</v>
       </c>
       <c r="L7" s="6">
         <v>4</v>
@@ -788,14 +788,14 @@
       <c r="N7" s="6">
         <v>60</v>
       </c>
-      <c r="O7" s="6">
-        <v>4</v>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1529</v>
+        <v>1647</v>
       </c>
       <c r="Q7" s="6">
-        <v>843</v>
+        <v>725</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -833,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>1029</v>
+        <v>1043</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -848,10 +848,10 @@
         <v>2</v>
       </c>
       <c r="P8" s="6">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="Q8" s="6">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -889,7 +889,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -901,13 +901,13 @@
         <v>22</v>
       </c>
       <c r="O9" s="6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P9" s="6">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="Q9" s="6">
-        <v>2721</v>
+        <v>2679</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1089,19 +1089,19 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="6">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
@@ -1113,25 +1113,25 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="L13" s="6">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="Q13" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1225,7 +1225,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>22</v>
@@ -1234,7 +1234,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1375,7 +1375,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1393,7 +1393,7 @@
         <v>22</v>
       </c>
       <c r="K18" s="6">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="L18" s="6">
         <v>54</v>
@@ -1408,10 +1408,10 @@
         <v>1</v>
       </c>
       <c r="P18" s="6">
-        <v>2247</v>
+        <v>2268</v>
       </c>
       <c r="Q18" s="6">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>45</v>
@@ -1537,7 +1537,7 @@
         <v>245</v>
       </c>
       <c r="C21" s="6">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>22</v>
@@ -1570,16 +1570,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="Q21" s="6">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>51</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="58">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,25 +88,25 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>69.44%</t>
+    <t>73.95%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>74.38%</t>
+    <t>78.94%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>14.82%</t>
+    <t>42.03%</t>
   </si>
   <si>
     <t>Palcos</t>
   </si>
   <si>
-    <t>82.88%</t>
+    <t>84.96%</t>
   </si>
   <si>
     <t>Palcos Superior</t>
@@ -142,19 +142,19 @@
     <t>Suites</t>
   </si>
   <si>
-    <t>67.32%</t>
+    <t>75.98%</t>
   </si>
   <si>
     <t>Superior</t>
   </si>
   <si>
-    <t>98.65%</t>
+    <t>99.52%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>98.30%</t>
+    <t>98.15%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
@@ -166,7 +166,7 @@
     <t>ToroBar</t>
   </si>
   <si>
-    <t>68.57%</t>
+    <t>72.24%</t>
   </si>
   <si>
     <t>ToroGrill</t>
@@ -184,7 +184,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>71.09%</t>
+    <t>78.05%</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -777,7 +777,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>1527</v>
+        <v>1662</v>
       </c>
       <c r="L7" s="6">
         <v>4</v>
@@ -788,14 +788,14 @@
       <c r="N7" s="6">
         <v>60</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="O7" s="6">
+        <v>3</v>
       </c>
       <c r="P7" s="6">
-        <v>1647</v>
+        <v>1754</v>
       </c>
       <c r="Q7" s="6">
-        <v>725</v>
+        <v>618</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -808,14 +808,14 @@
       <c r="B8" s="6">
         <v>2170</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
+      <c r="C8" s="6">
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -833,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>1043</v>
+        <v>1132</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -842,16 +842,16 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="O8" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P8" s="6">
-        <v>1614</v>
+        <v>1713</v>
       </c>
       <c r="Q8" s="6">
-        <v>556</v>
+        <v>457</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -889,7 +889,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -897,17 +897,17 @@
       <c r="M9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O9" s="6">
-        <v>12</v>
+      <c r="N9" s="6">
+        <v>819</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>466</v>
+        <v>1322</v>
       </c>
       <c r="Q9" s="6">
-        <v>2679</v>
+        <v>1823</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -918,7 +918,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="6">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C10" s="6">
         <v>10</v>
@@ -927,7 +927,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -960,10 +960,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="Q10" s="6">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -1095,7 +1095,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1113,7 +1113,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="L13" s="6">
         <v>97</v>
@@ -1122,7 +1122,7 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
@@ -1225,7 +1225,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>22</v>
@@ -1234,7 +1234,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1319,7 +1319,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="6">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1352,10 +1352,10 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="Q17" s="6">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>43</v>
@@ -1369,13 +1369,13 @@
         <v>2299</v>
       </c>
       <c r="C18" s="6">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>527</v>
+        <v>580</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1393,7 +1393,7 @@
         <v>22</v>
       </c>
       <c r="K18" s="6">
-        <v>872</v>
+        <v>891</v>
       </c>
       <c r="L18" s="6">
         <v>54</v>
@@ -1402,16 +1402,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>405</v>
-      </c>
-      <c r="O18" s="6">
-        <v>1</v>
+        <v>304</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2268</v>
+        <v>2288</v>
       </c>
       <c r="Q18" s="6">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>45</v>
@@ -1449,7 +1449,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L19" s="6">
         <v>8</v>
@@ -1458,16 +1458,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="Q19" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>47</v>
@@ -1543,7 +1543,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="6">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1576,10 +1576,10 @@
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="Q21" s="6">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>51</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="58">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,19 +88,19 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>73.95%</t>
+    <t>86.76%</t>
   </si>
   <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>78.94%</t>
+    <t>88.39%</t>
   </si>
   <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>42.03%</t>
+    <t>80.29%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -124,7 +124,7 @@
     <t>Preferente</t>
   </si>
   <si>
-    <t>99.78%</t>
+    <t>99.89%</t>
   </si>
   <si>
     <t>Preferente1raBase</t>
@@ -142,19 +142,19 @@
     <t>Suites</t>
   </si>
   <si>
-    <t>75.98%</t>
+    <t>79.92%</t>
   </si>
   <si>
     <t>Superior</t>
   </si>
   <si>
-    <t>99.52%</t>
+    <t>99.87%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>98.15%</t>
+    <t>98.61%</t>
   </si>
   <si>
     <t>Superior3raBase</t>
@@ -166,7 +166,7 @@
     <t>ToroBar</t>
   </si>
   <si>
-    <t>72.24%</t>
+    <t>75.10%</t>
   </si>
   <si>
     <t>ToroGrill</t>
@@ -178,13 +178,13 @@
     <t>Zona Móbil</t>
   </si>
   <si>
-    <t>38.46%</t>
+    <t>40.00%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>78.05%</t>
+    <t>88.89%</t>
   </si>
 </sst>
 </file>
@@ -752,14 +752,14 @@
       <c r="B7" s="6">
         <v>2372</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
+      <c r="C7" s="6">
+        <v>35</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -777,10 +777,10 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>1662</v>
+        <v>1894</v>
       </c>
       <c r="L7" s="6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
@@ -789,13 +789,13 @@
         <v>60</v>
       </c>
       <c r="O7" s="6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="P7" s="6">
-        <v>1754</v>
+        <v>2058</v>
       </c>
       <c r="Q7" s="6">
-        <v>618</v>
+        <v>314</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -809,13 +809,13 @@
         <v>2170</v>
       </c>
       <c r="C8" s="6">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -833,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>1132</v>
+        <v>1236</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -844,14 +844,14 @@
       <c r="N8" s="6">
         <v>534</v>
       </c>
-      <c r="O8" s="6">
-        <v>6</v>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1713</v>
+        <v>1918</v>
       </c>
       <c r="Q8" s="6">
-        <v>457</v>
+        <v>252</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -864,8 +864,8 @@
       <c r="B9" s="6">
         <v>3145</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
+      <c r="C9" s="6">
+        <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -889,7 +889,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>503</v>
+        <v>631</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -898,16 +898,16 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>819</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
+        <v>1880</v>
+      </c>
+      <c r="O9" s="6">
+        <v>4</v>
       </c>
       <c r="P9" s="6">
-        <v>1322</v>
+        <v>2525</v>
       </c>
       <c r="Q9" s="6">
-        <v>1823</v>
+        <v>620</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1089,13 +1089,13 @@
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1113,7 +1113,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="L13" s="6">
         <v>97</v>
@@ -1122,16 +1122,16 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="Q13" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1225,16 +1225,16 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>534</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>22</v>
+        <v>537</v>
+      </c>
+      <c r="L15" s="6">
+        <v>60</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1319,7 +1319,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="6">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1352,10 +1352,10 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="Q17" s="6">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>43</v>
@@ -1369,19 +1369,19 @@
         <v>2299</v>
       </c>
       <c r="C18" s="6">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>580</v>
+        <v>657</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>22</v>
@@ -1393,7 +1393,7 @@
         <v>22</v>
       </c>
       <c r="K18" s="6">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="L18" s="6">
         <v>54</v>
@@ -1402,16 +1402,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>304</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>22</v>
+        <v>193</v>
+      </c>
+      <c r="O18" s="6">
+        <v>1</v>
       </c>
       <c r="P18" s="6">
-        <v>2288</v>
+        <v>2296</v>
       </c>
       <c r="Q18" s="6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>45</v>
@@ -1449,7 +1449,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L19" s="6">
         <v>8</v>
@@ -1460,14 +1460,14 @@
       <c r="N19" s="6">
         <v>46</v>
       </c>
-      <c r="O19" s="6" t="s">
-        <v>22</v>
+      <c r="O19" s="6">
+        <v>2</v>
       </c>
       <c r="P19" s="6">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="Q19" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>47</v>
@@ -1543,7 +1543,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="6">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1576,10 +1576,10 @@
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Q21" s="6">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>51</v>
@@ -1649,7 +1649,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
@@ -1688,10 +1688,10 @@
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q23" s="6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>55</v>

--- a/data/asistencia/Toros 2026.xlsx
+++ b/data/asistencia/Toros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="53">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,45 +88,36 @@
     <t>General Preferente</t>
   </si>
   <si>
-    <t>86.76%</t>
-  </si>
-  <si>
     <t>General Superior</t>
   </si>
   <si>
-    <t>88.39%</t>
-  </si>
-  <si>
     <t>Jardines</t>
   </si>
   <si>
-    <t>80.29%</t>
+    <t>85.17%</t>
   </si>
   <si>
     <t>Palcos</t>
   </si>
   <si>
-    <t>84.96%</t>
+    <t>91.45%</t>
   </si>
   <si>
     <t>Palcos Superior</t>
   </si>
   <si>
-    <t>73.68%</t>
+    <t>84.21%</t>
   </si>
   <si>
     <t>PalcosLaterales</t>
   </si>
   <si>
-    <t>56.00%</t>
+    <t>80.00%</t>
   </si>
   <si>
     <t>Preferente</t>
   </si>
   <si>
-    <t>99.89%</t>
-  </si>
-  <si>
     <t>Preferente1raBase</t>
   </si>
   <si>
@@ -136,7 +127,7 @@
     <t>Suite ToroGrill</t>
   </si>
   <si>
-    <t>50.00%</t>
+    <t>75.00%</t>
   </si>
   <si>
     <t>Suites</t>
@@ -148,43 +139,37 @@
     <t>Superior</t>
   </si>
   <si>
-    <t>99.87%</t>
+    <t>99.83%</t>
   </si>
   <si>
     <t>Superior1raBase</t>
   </si>
   <si>
-    <t>98.61%</t>
-  </si>
-  <si>
     <t>Superior3raBase</t>
   </si>
   <si>
-    <t>97.84%</t>
-  </si>
-  <si>
     <t>ToroBar</t>
   </si>
   <si>
-    <t>75.10%</t>
+    <t>98.37%</t>
   </si>
   <si>
     <t>ToroGrill</t>
   </si>
   <si>
-    <t>12.21%</t>
+    <t>19.20%</t>
   </si>
   <si>
     <t>Zona Móbil</t>
   </si>
   <si>
-    <t>40.00%</t>
+    <t>43.08%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>88.89%</t>
+    <t>93.86%</t>
   </si>
 </sst>
 </file>
@@ -702,8 +687,8 @@
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
+      <c r="E6" s="6">
+        <v>255</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -730,7 +715,7 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
@@ -753,13 +738,13 @@
         <v>2372</v>
       </c>
       <c r="C7" s="6">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -777,7 +762,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>1894</v>
+        <v>2021</v>
       </c>
       <c r="L7" s="6">
         <v>24</v>
@@ -786,36 +771,36 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>60</v>
-      </c>
-      <c r="O7" s="6">
-        <v>16</v>
+        <v>45</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>2058</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>314</v>
+        <v>2372</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>2170</v>
       </c>
       <c r="C8" s="6">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>51</v>
+        <v>396</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -833,45 +818,45 @@
         <v>22</v>
       </c>
       <c r="K8" s="6">
-        <v>1236</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>22</v>
+        <v>1364</v>
+      </c>
+      <c r="L8" s="6">
+        <v>12</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>534</v>
+        <v>95</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1918</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>252</v>
+        <v>2170</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="6">
-        <v>3145</v>
+        <v>5145</v>
       </c>
       <c r="C9" s="6">
-        <v>10</v>
+        <v>2420</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+      <c r="E9" s="6">
+        <v>121</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -889,7 +874,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>631</v>
+        <v>942</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -898,24 +883,24 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>1880</v>
-      </c>
-      <c r="O9" s="6">
-        <v>4</v>
+        <v>899</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>2525</v>
+        <v>4382</v>
       </c>
       <c r="Q9" s="6">
-        <v>620</v>
+        <v>763</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>339</v>
@@ -927,7 +912,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -960,30 +945,30 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="Q10" s="6">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6">
         <v>95</v>
       </c>
       <c r="C11" s="6">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6">
         <v>15</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6">
-        <v>10</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -1016,18 +1001,18 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Q11" s="6">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>50</v>
@@ -1038,8 +1023,8 @@
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
+      <c r="E12" s="6">
+        <v>40</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1050,8 +1035,8 @@
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="6">
-        <v>28</v>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1072,30 +1057,30 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q12" s="6">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
         <v>1794</v>
       </c>
       <c r="C13" s="6">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1113,7 +1098,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="L13" s="6">
         <v>97</v>
@@ -1122,24 +1107,24 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>189</v>
+        <v>42</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>1792</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>2</v>
+        <v>1794</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6">
         <v>499</v>
@@ -1195,13 +1180,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6">
         <v>671</v>
       </c>
       <c r="C15" s="6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
@@ -1225,7 +1210,7 @@
         <v>22</v>
       </c>
       <c r="K15" s="6">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="L15" s="6">
         <v>60</v>
@@ -1234,7 +1219,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1251,7 +1236,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6">
         <v>40</v>
@@ -1262,8 +1247,8 @@
       <c r="D16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>22</v>
+      <c r="E16" s="6">
+        <v>10</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1296,18 +1281,18 @@
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Q16" s="6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" s="6">
         <v>254</v>
@@ -1319,7 +1304,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="6">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1331,7 +1316,7 @@
         <v>22</v>
       </c>
       <c r="I17" s="6">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1358,24 +1343,24 @@
         <v>51</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6">
         <v>2299</v>
       </c>
       <c r="C18" s="6">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>657</v>
+        <v>756</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1393,39 +1378,39 @@
         <v>22</v>
       </c>
       <c r="K18" s="6">
-        <v>905</v>
+        <v>927</v>
       </c>
       <c r="L18" s="6">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>193</v>
-      </c>
-      <c r="O18" s="6">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="Q18" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B19" s="6">
         <v>648</v>
       </c>
       <c r="C19" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
@@ -1449,7 +1434,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="6">
-        <v>560</v>
+        <v>601</v>
       </c>
       <c r="L19" s="6">
         <v>8</v>
@@ -1458,30 +1443,30 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>46</v>
-      </c>
-      <c r="O19" s="6">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>639</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>9</v>
+        <v>648</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B20" s="6">
         <v>786</v>
       </c>
       <c r="C20" s="6">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>22</v>
@@ -1493,7 +1478,7 @@
         <v>22</v>
       </c>
       <c r="G20" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
@@ -1505,7 +1490,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="6">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L20" s="6">
         <v>2</v>
@@ -1513,25 +1498,25 @@
       <c r="M20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="6">
-        <v>6</v>
+      <c r="N20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>769</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>17</v>
+        <v>786</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6">
         <v>245</v>
@@ -1543,7 +1528,7 @@
         <v>22</v>
       </c>
       <c r="E21" s="6">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1569,31 +1554,31 @@
       <c r="M21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N21" s="6">
-        <v>2</v>
+      <c r="N21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="Q21" s="6">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B22" s="6">
-        <v>344</v>
+        <v>224</v>
       </c>
       <c r="C22" s="6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>22</v>
@@ -1632,24 +1617,24 @@
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q22" s="6">
-        <v>302</v>
+        <v>181</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B23" s="6">
         <v>65</v>
       </c>
       <c r="C23" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
@@ -1688,18 +1673,18 @@
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q23" s="6">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B24" s="7">
         <f>SUM(B6:B23)</f>
@@ -1750,7 +1735,7 @@
         <f>SUM(Q6:Q23)</f>
       </c>
       <c r="R24" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
